--- a/NRCS/Output/NRCS_Timetable_Final.xlsx
+++ b/NRCS/Output/NRCS_Timetable_Final.xlsx
@@ -656,27 +656,23 @@
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
+      <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -703,20 +699,16 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -731,22 +723,26 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
@@ -762,18 +758,18 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr"/>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -802,24 +798,24 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
+      <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -836,31 +832,35 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -935,22 +935,14 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Class 9 (PHY)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
       <c r="H14" s="7" t="inlineStr"/>
@@ -962,17 +954,13 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Class 10 (CHEM)</t>
@@ -989,12 +977,12 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
       <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr"/>
@@ -1008,14 +996,22 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (PHY)</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
@@ -1029,14 +1025,14 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 9 (PHY)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr"/>
       <c r="D18" s="7" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
@@ -1053,13 +1049,17 @@
       <c r="B19" s="7" t="inlineStr"/>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
@@ -1138,21 +1138,9 @@
       <c r="B23" s="7" t="inlineStr"/>
       <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
+      <c r="E23" s="7" t="inlineStr"/>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
@@ -1165,18 +1153,14 @@
       <c r="B24" s="7" t="inlineStr"/>
       <c r="C24" s="7" t="inlineStr"/>
       <c r="D24" s="7" t="inlineStr"/>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="I24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1188,14 +1172,22 @@
       <c r="B25" s="7" t="inlineStr"/>
       <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Class 8 (BIO)</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1210,7 +1202,11 @@
       <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="7" t="inlineStr"/>
       <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
       <c r="I26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1223,13 +1219,13 @@
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
+      <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="I27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1244,13 +1240,17 @@
       <c r="E28" s="7" t="inlineStr"/>
       <c r="F28" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr"/>
@@ -1323,27 +1323,27 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr"/>
+      <c r="C32" s="7" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr"/>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr"/>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -1358,24 +1358,24 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr"/>
-      <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
       <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
+      <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
@@ -1393,29 +1393,29 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
       <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1431,24 +1431,24 @@
       <c r="B35" s="7" t="inlineStr"/>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 9 (TEL)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (TEL)</t>
+          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -1469,12 +1469,12 @@
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr"/>
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr"/>
       <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
@@ -1498,29 +1498,29 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
+      <c r="B37" s="7" t="inlineStr"/>
       <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1600,22 +1600,26 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
       <c r="F41" s="7" t="inlineStr"/>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
+          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
@@ -1635,28 +1639,28 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1674,24 +1678,28 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr"/>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
       <c r="D43" s="7" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1706,17 +1714,17 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (G.K)</t>
+          <t>Class 8 (HIN)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr"/>
@@ -1724,7 +1732,7 @@
       <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -1741,31 +1749,27 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (HIN)</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
+          <t>Class 8 (G.K)</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr"/>
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr"/>
       <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (G.K)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1786,25 +1790,21 @@
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
+      <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1885,8 +1885,16 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr"/>
-      <c r="E50" s="7" t="inlineStr"/>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr"/>
       <c r="H50" s="7" t="inlineStr"/>
@@ -1904,11 +1912,7 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="D51" s="7" t="inlineStr"/>
       <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (MATH)</t>
+          <t>Class 10 (MATH)</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
@@ -1974,12 +1978,12 @@
       <c r="B54" s="7" t="inlineStr"/>
       <c r="C54" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -1999,11 +2003,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr"/>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
-        </is>
-      </c>
+      <c r="C55" s="7" t="inlineStr"/>
       <c r="D55" s="7" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
+          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
@@ -2090,28 +2090,28 @@
       <c r="B59" s="7" t="inlineStr"/>
       <c r="C59" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr"/>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (PHY)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -2140,17 +2140,17 @@
       <c r="E60" s="7" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr"/>
@@ -2164,7 +2164,7 @@
       <c r="B61" s="7" t="inlineStr"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -2174,18 +2174,18 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr"/>
@@ -2196,31 +2196,27 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
+      <c r="B62" s="7" t="inlineStr"/>
       <c r="C62" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr"/>
       <c r="E62" s="7" t="inlineStr">
         <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
+      <c r="F62" s="7" t="inlineStr"/>
       <c r="G62" s="7" t="inlineStr"/>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr"/>
@@ -2231,31 +2227,35 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr"/>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr"/>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr"/>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
@@ -2379,18 +2379,18 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 1 (GRAM)</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (GRAM)</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -2428,17 +2428,17 @@
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
@@ -2460,23 +2460,23 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (GRAM)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
+          <t>Class 3 (GRAM)</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -2503,15 +2503,15 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
           <t>Class 4 (ENG)</t>
         </is>
       </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
           <t>Class 3 (ENG)</t>
@@ -2520,7 +2520,7 @@
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
+          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 5 (GRAM)</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -2553,17 +2553,17 @@
       <c r="E72" s="7" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (GRAM)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
+          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -2585,28 +2585,28 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (GRAM)</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (GRAM)</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -2692,10 +2692,14 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="7" t="inlineStr"/>
@@ -2712,12 +2716,12 @@
           <t>Class 4 (COMP)</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr"/>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr"/>
       <c r="F78" s="7" t="inlineStr"/>
       <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr"/>
@@ -2730,21 +2734,13 @@
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr"/>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
+      <c r="C79" s="7" t="inlineStr"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
+      <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr"/>
       <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr"/>
@@ -2757,13 +2753,13 @@
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr"/>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr"/>
+      <c r="D80" s="7" t="inlineStr"/>
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
       <c r="H80" s="7" t="inlineStr"/>
@@ -2776,13 +2772,13 @@
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr"/>
-      <c r="C81" s="7" t="inlineStr"/>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
       <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="E81" s="7" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr"/>
@@ -2795,7 +2791,11 @@
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr"/>
-      <c r="C82" s="7" t="inlineStr"/>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
       <c r="D82" s="7" t="inlineStr"/>
       <c r="E82" s="7" t="inlineStr">
         <is>
@@ -2883,18 +2883,18 @@
       <c r="C86" s="7" t="inlineStr"/>
       <c r="D86" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
+          <t>U.K.G (TEL)</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr"/>
@@ -2915,18 +2915,26 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr"/>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="D87" s="7" t="inlineStr"/>
       <c r="E87" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
+          <t>Class 1 (G.K)</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -2946,28 +2954,24 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
+      <c r="C88" s="7" t="inlineStr"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr"/>
       <c r="F88" s="7" t="inlineStr"/>
       <c r="G88" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="H88" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
+      <c r="H88" s="7" t="inlineStr"/>
       <c r="I88" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -2996,13 +3000,13 @@
           <t>L.K.G (TEL)</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3017,27 +3021,31 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (TEL)</t>
+          <t>Class 1 (G.K)</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (TEL)</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3052,31 +3060,23 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr"/>
+      <c r="C91" s="7" t="inlineStr"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
       <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
+      <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3158,26 +3158,26 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr"/>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr"/>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3203,18 +3203,18 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -3237,23 +3237,23 @@
       <c r="C97" s="7" t="inlineStr"/>
       <c r="D97" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
@@ -3273,26 +3273,26 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr"/>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr"/>
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -3318,17 +3318,17 @@
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr"/>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
+      <c r="G99" s="7" t="inlineStr"/>
       <c r="H99" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
@@ -3351,28 +3351,28 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr"/>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr"/>
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="F100" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr"/>
       <c r="G100" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
+      <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3453,19 +3453,19 @@
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr"/>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr"/>
+      <c r="E104" s="7" t="inlineStr"/>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (GRAM)</t>
+        </is>
+      </c>
       <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (GRAM)</t>
-        </is>
-      </c>
+      <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
@@ -3475,24 +3475,24 @@
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr"/>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr"/>
+      <c r="D105" s="7" t="inlineStr"/>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (ENG)</t>
+          <t>Class 10 (GRAM)</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (GRAM)</t>
-        </is>
-      </c>
+      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3508,10 +3508,14 @@
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr"/>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (ENG)</t>
+          <t>Class 8 (GRAM)</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr"/>
@@ -3525,22 +3529,18 @@
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr"/>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr"/>
+      <c r="D107" s="7" t="inlineStr"/>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (GRAM)</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr"/>
       <c r="G107" s="7" t="inlineStr"/>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
@@ -3560,13 +3560,17 @@
       <c r="D108" s="7" t="inlineStr"/>
       <c r="E108" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (GRAM)</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr"/>
@@ -3585,18 +3589,14 @@
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr"/>
-      <c r="E109" s="7" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr"/>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr"/>
+      <c r="H109" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (GRAM)</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr"/>
-      <c r="H109" s="7" t="inlineStr"/>
       <c r="I109" s="7" t="inlineStr"/>
     </row>
     <row r="111">
@@ -3667,22 +3667,18 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr"/>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
+      <c r="D113" s="7" t="inlineStr"/>
+      <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr"/>
       <c r="G113" s="7" t="inlineStr"/>
       <c r="H113" s="7" t="inlineStr"/>
@@ -3694,16 +3690,20 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr"/>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr"/>
-      <c r="D114" s="7" t="inlineStr"/>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
@@ -3720,7 +3720,7 @@
       <c r="B115" s="7" t="inlineStr"/>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
@@ -3767,15 +3767,11 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="B117" s="7" t="inlineStr"/>
       <c r="C117" s="7" t="inlineStr"/>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -3794,13 +3790,17 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr"/>
-      <c r="C118" s="7" t="inlineStr"/>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
@@ -3881,35 +3881,31 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr"/>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (EVS)</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr"/>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (G.K)</t>
-        </is>
-      </c>
-      <c r="H122" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
+      <c r="H122" s="7" t="inlineStr"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3924,23 +3920,23 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
@@ -3972,28 +3968,28 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H124" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
@@ -4010,21 +4006,25 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr"/>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr"/>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr"/>
       <c r="G125" s="7" t="inlineStr">
         <is>
           <t>U.K.G (ENG)</t>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="I125" s="8" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -4065,12 +4065,12 @@
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -4102,23 +4102,23 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="I127" s="8" t="inlineStr">
@@ -4200,24 +4200,32 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr"/>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (G.K)</t>
+        </is>
+      </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr"/>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (COMP)</t>
-        </is>
-      </c>
-      <c r="F131" s="7" t="inlineStr">
+      <c r="G131" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="G131" s="7" t="inlineStr"/>
-      <c r="H131" s="7" t="inlineStr"/>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4230,18 +4238,22 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr"/>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr"/>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr"/>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (G.K)</t>
+        </is>
+      </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
@@ -4252,11 +4264,7 @@
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
+      <c r="H132" s="7" t="inlineStr"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4276,26 +4284,22 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 7 (COMP)</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr"/>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (G.K)</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (COMP)</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="inlineStr">
-        <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="H133" s="7" t="inlineStr"/>
+      <c r="F133" s="7" t="inlineStr"/>
+      <c r="G133" s="7" t="inlineStr"/>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="I133" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4308,23 +4312,23 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr"/>
-      <c r="C134" s="7" t="inlineStr"/>
-      <c r="D134" s="7" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
+      <c r="D134" s="7" t="inlineStr"/>
       <c r="E134" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
+      <c r="F134" s="7" t="inlineStr"/>
       <c r="G134" s="7" t="inlineStr"/>
       <c r="H134" s="7" t="inlineStr"/>
       <c r="I134" s="8" t="inlineStr">
@@ -4339,12 +4343,12 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (G.K)</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="inlineStr"/>
+      <c r="B135" s="7" t="inlineStr"/>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (G.K)</t>
+        </is>
+      </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
           <t>Class 6 (MATH)</t>
@@ -4352,7 +4356,7 @@
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (G.K)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
@@ -4361,11 +4365,7 @@
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="H135" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
+      <c r="H135" s="7" t="inlineStr"/>
       <c r="I135" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4378,27 +4378,27 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="B136" s="7" t="inlineStr"/>
+      <c r="C136" s="7" t="inlineStr"/>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
         <is>
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="D136" s="7" t="inlineStr"/>
-      <c r="E136" s="7" t="inlineStr">
+      <c r="F136" s="7" t="inlineStr"/>
+      <c r="G136" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr"/>
-      <c r="G136" s="7" t="inlineStr"/>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="I136" s="8" t="inlineStr">
@@ -4477,24 +4477,28 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="D140" s="7" t="inlineStr"/>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="F140" s="7" t="inlineStr"/>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr"/>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
@@ -4516,17 +4520,13 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="C141" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
@@ -4567,21 +4567,25 @@
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr"/>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="inlineStr"/>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr"/>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I142" s="8" t="inlineStr">
@@ -4603,28 +4607,28 @@
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="H143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I143" s="8" t="inlineStr">
@@ -4641,35 +4645,31 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr"/>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr"/>
       <c r="I144" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4684,33 +4684,33 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr"/>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="H145" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="D145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr"/>
-      <c r="F145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="I145" s="8" t="inlineStr">
@@ -4791,10 +4791,14 @@
       <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="7" t="inlineStr"/>
       <c r="E149" s="7" t="inlineStr"/>
-      <c r="F149" s="7" t="inlineStr"/>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (ENG)</t>
+          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="H149" s="7" t="inlineStr">
@@ -4802,11 +4806,7 @@
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="I149" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
+      <c r="I149" s="7" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -4823,17 +4823,17 @@
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G150" s="7" t="inlineStr"/>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="I150" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
+      <c r="I150" s="7" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -4855,12 +4855,12 @@
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="H151" s="7" t="inlineStr"/>
-      <c r="I151" s="8" t="inlineStr">
+      <c r="H151" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
+      <c r="I151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -4874,13 +4874,13 @@
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (ENG)</t>
+          <t>Class 8 (ENG)</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr"/>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (ENG)</t>
+          <t>Class 9 (ENG)</t>
         </is>
       </c>
       <c r="I152" s="8" t="inlineStr">
@@ -4909,12 +4909,12 @@
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="H153" s="7" t="inlineStr"/>
-      <c r="I153" s="8" t="inlineStr">
+      <c r="H153" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
+      <c r="I153" s="7" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -4926,17 +4926,17 @@
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="7" t="inlineStr"/>
       <c r="E154" s="7" t="inlineStr"/>
-      <c r="F154" s="7" t="inlineStr"/>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
+      <c r="H154" s="7" t="inlineStr"/>
       <c r="I154" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
@@ -5011,7 +5011,11 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B158" s="7" t="inlineStr"/>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
@@ -5019,14 +5023,10 @@
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="inlineStr">
-        <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
+      <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="7" t="inlineStr"/>
       <c r="G158" s="7" t="inlineStr"/>
       <c r="H158" s="7" t="inlineStr"/>
@@ -5038,22 +5038,22 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B159" s="7" t="inlineStr"/>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="D159" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="E159" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
+      <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="7" t="inlineStr"/>
       <c r="G159" s="7" t="inlineStr"/>
       <c r="H159" s="7" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
@@ -5099,13 +5099,13 @@
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr"/>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
@@ -5119,10 +5119,14 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B162" s="7" t="inlineStr"/>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
@@ -5130,11 +5134,7 @@
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="E162" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
+      <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="7" t="inlineStr"/>
       <c r="G162" s="7" t="inlineStr"/>
       <c r="H162" s="7" t="inlineStr"/>
@@ -5148,20 +5148,20 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr"/>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="C163" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="D163" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="7" t="inlineStr"/>
       <c r="G163" s="7" t="inlineStr"/>
       <c r="H163" s="7" t="inlineStr"/>
@@ -5240,23 +5240,23 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr"/>
-      <c r="D167" s="7" t="inlineStr">
+      <c r="C167" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
+      <c r="D167" s="7" t="inlineStr"/>
       <c r="E167" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="F167" s="7" t="inlineStr"/>
-      <c r="G167" s="7" t="inlineStr">
+      <c r="F167" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
+      <c r="G167" s="7" t="inlineStr"/>
       <c r="H167" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
@@ -5279,28 +5279,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C168" s="7" t="inlineStr">
+      <c r="C168" s="7" t="inlineStr"/>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="D168" s="7" t="inlineStr"/>
-      <c r="E168" s="7" t="inlineStr">
+      <c r="F168" s="7" t="inlineStr"/>
+      <c r="G168" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="G168" s="7" t="inlineStr">
+      <c r="H168" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="H168" s="7" t="inlineStr"/>
       <c r="I168" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5318,12 +5318,12 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C169" s="7" t="inlineStr">
+      <c r="C169" s="7" t="inlineStr"/>
+      <c r="D169" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D169" s="7" t="inlineStr"/>
       <c r="E169" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
@@ -5331,13 +5331,13 @@
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
+          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr"/>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
+          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="I169" s="8" t="inlineStr">
@@ -5357,26 +5357,26 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C170" s="7" t="inlineStr">
+      <c r="C170" s="7" t="inlineStr"/>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="D170" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr"/>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr"/>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
+          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="I170" s="8" t="inlineStr">
@@ -5396,24 +5396,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C171" s="7" t="inlineStr">
+      <c r="C171" s="7" t="inlineStr"/>
+      <c r="D171" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr">
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr"/>
+      <c r="G171" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="E171" s="7" t="inlineStr"/>
-      <c r="F171" s="7" t="inlineStr">
+      <c r="H171" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr"/>
-      <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5426,21 +5430,21 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B172" s="7" t="inlineStr"/>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D172" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
+      <c r="D172" s="7" t="inlineStr"/>
       <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (TEL)</t>
+          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
@@ -5448,11 +5452,7 @@
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="H172" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
+      <c r="H172" s="7" t="inlineStr"/>
       <c r="I172" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5532,26 +5532,26 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C176" s="7" t="inlineStr"/>
-      <c r="D176" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr"/>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="I176" s="8" t="inlineStr">
@@ -5566,33 +5566,29 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B177" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
+      <c r="B177" s="7" t="inlineStr"/>
       <c r="C177" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr"/>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="D177" s="7" t="inlineStr">
+      <c r="F177" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="E177" s="7" t="inlineStr"/>
-      <c r="F177" s="7" t="inlineStr"/>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="inlineStr">
-        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
+      <c r="H177" s="7" t="inlineStr"/>
       <c r="I177" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5612,24 +5608,24 @@
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr"/>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D178" s="7" t="inlineStr">
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr"/>
+      <c r="H178" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr"/>
-      <c r="F178" s="7" t="inlineStr"/>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="H178" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="I178" s="8" t="inlineStr">
@@ -5651,16 +5647,20 @@
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr"/>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="D179" s="7" t="inlineStr"/>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="F179" s="7" t="inlineStr"/>
       <c r="G179" s="7" t="inlineStr"/>
       <c r="H179" s="7" t="inlineStr">
         <is>
@@ -5686,21 +5686,21 @@
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D180" s="7" t="inlineStr"/>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="F180" s="7" t="inlineStr">
+      <c r="E180" s="7" t="inlineStr"/>
+      <c r="F180" s="7" t="inlineStr"/>
+      <c r="G180" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="G180" s="7" t="inlineStr"/>
       <c r="H180" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
@@ -5726,17 +5726,17 @@
       <c r="C181" s="7" t="inlineStr"/>
       <c r="D181" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="G181" s="7" t="inlineStr"/>
@@ -5821,13 +5821,17 @@
       <c r="E185" s="7" t="inlineStr"/>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="G185" s="7" t="inlineStr"/>
+          <t>Class 7 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (P.E.T)</t>
+        </is>
+      </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="I185" s="7" t="inlineStr"/>
@@ -5844,15 +5848,19 @@
       <c r="E186" s="7" t="inlineStr"/>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (P.E.T)</t>
+          <t>Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H186" s="7" t="inlineStr"/>
+          <t>Class 9 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I186" s="7" t="inlineStr"/>
     </row>
     <row r="187">
@@ -5867,19 +5875,15 @@
       <c r="E187" s="7" t="inlineStr"/>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (P.E.T)</t>
+          <t>Class 2 (P.E.T)</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H187" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (P.E.T)</t>
-        </is>
-      </c>
+          <t>Class 5 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr"/>
       <c r="I187" s="7" t="inlineStr"/>
     </row>
     <row r="188">
@@ -5894,15 +5898,11 @@
       <c r="E188" s="7" t="inlineStr"/>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (P.E.T)</t>
+          <t>Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr"/>
-      <c r="H188" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="H188" s="7" t="inlineStr"/>
       <c r="I188" s="7" t="inlineStr"/>
     </row>
     <row r="189">
@@ -5917,17 +5917,13 @@
       <c r="E189" s="7" t="inlineStr"/>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="G189" s="7" t="inlineStr">
-        <is>
           <t>Class 5 (P.E.T)</t>
         </is>
       </c>
+      <c r="G189" s="7" t="inlineStr"/>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (P.E.T)</t>
+          <t>L.K.G (P.E.T)</t>
         </is>
       </c>
       <c r="I189" s="7" t="inlineStr"/>
@@ -5942,15 +5938,15 @@
       <c r="C190" s="7" t="inlineStr"/>
       <c r="D190" s="7" t="inlineStr"/>
       <c r="E190" s="7" t="inlineStr"/>
-      <c r="F190" s="7" t="inlineStr"/>
-      <c r="G190" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (P.E.T)</t>
-        </is>
-      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr"/>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 8 (P.E.T)</t>
         </is>
       </c>
       <c r="I190" s="7" t="inlineStr"/>
@@ -6250,7 +6246,7 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -6268,7 +6264,7 @@
       <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -6309,14 +6305,14 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>Bheema
-(PHY)</t>
+          <t>Riya
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -6328,19 +6324,19 @@
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
+          <t>Swathi
+(HIN)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -6351,44 +6347,44 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(G.K)</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -6405,28 +6401,28 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Maheswari
@@ -6435,44 +6431,44 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Maha
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
 (ENG)</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(BIO)</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(CHEM)</t>
-        </is>
-      </c>
       <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -6483,32 +6479,32 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(EVS)</t>
+        </is>
+      </c>
       <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Maheswari
 (COMP)</t>
         </is>
       </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -6519,38 +6515,38 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(PHY)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(COMP)</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -6561,74 +6557,73 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Maha
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
 (ENG)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
+          <t>Ravi
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -6640,73 +6635,73 @@
       <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(G.K)</t>
+          <t>Maha
+(ENG)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(CHEM)</t>
-        </is>
-      </c>
       <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -6723,8 +6718,8 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -6735,26 +6730,26 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>Fathima
+(HIN)</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -6765,26 +6760,26 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>Lalitha
+(CHEM)</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(COMP)</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
         </is>
       </c>
     </row>
@@ -6861,10 +6856,9 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6874,7 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -6898,7 +6892,7 @@
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -6909,8 +6903,8 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>Lalitha
+(EVS)</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -6921,8 +6915,8 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(BIO)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -6939,14 +6933,14 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>Riya
-(HIN)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Bheema
-(PHY)</t>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -6957,14 +6951,14 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(MATH)</t>
+          <t>Naga mani
+(TEL)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(HIN)</t>
+          <t>Sai Lakshmi
+(ENG)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -6975,16 +6969,16 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Maheswari
@@ -6993,32 +6987,32 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>Lalitha
+(EVS)</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(PHY)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -7036,7 +7030,7 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -7048,7 +7042,7 @@
       <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -7071,38 +7065,38 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>Swathi
+(TEL)</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>Maheswari
+(COMP)</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Fathima
+(HIN)</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>Sunitha
 (SOC)</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -7119,62 +7113,62 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
+          <t>Swathi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
 (G.K)</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
@@ -7197,50 +7191,50 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+(BIO)</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -7255,9 +7249,10 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(GRAM)</t>
         </is>
       </c>
     </row>
@@ -7280,46 +7275,46 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (CHEM)</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
@@ -7328,14 +7323,14 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Chalapathi
-(BIO)</t>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7342,7 @@
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -7358,44 +7353,44 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
+          <t>Naga mani
+(G.K)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Lalitha
+(BIO)</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -7406,8 +7401,8 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(GRAM)</t>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
@@ -7490,10 +7485,9 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7509,7 @@
       <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -7568,14 +7562,14 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7592,68 +7586,68 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(G.K)</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(BIO)</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
 (COMP)</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(PHY)</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
 (MATH)</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(PHY)</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -7664,50 +7658,50 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -7742,8 +7736,8 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(ENG)</t>
+          <t>Naga mani
+(TEL)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -7760,22 +7754,22 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Maheswari
-(COMP)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(G.K)</t>
-        </is>
-      </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Fathima
@@ -7784,32 +7778,32 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
-        </is>
-      </c>
       <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -7820,62 +7814,62 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(COMP)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -7886,8 +7880,8 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -7899,21 +7893,21 @@
       <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Naga mani
@@ -7922,43 +7916,44 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
+          <t>Sai Lakshmi
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+(PHY)</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
@@ -7975,13 +7970,13 @@
       <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (ENG)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -7992,55 +7987,55 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
       <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Chalapathi
 (BIO)</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="N24" s="12" t="inlineStr">
+      <c r="M24" s="12" t="inlineStr">
         <is>
           <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -8117,10 +8112,9 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8136,7 @@
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -8154,7 +8148,7 @@
       <c r="F26" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -8177,8 +8171,8 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(BIO)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -8190,7 +8184,7 @@
       <c r="L26" s="7" t="inlineStr">
         <is>
           <t>Fathima
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -8199,9 +8193,10 @@
 (SOC)</t>
         </is>
       </c>
-      <c r="N26" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8208,7 @@
       <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -8224,62 +8219,62 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(CHEM)</t>
+        </is>
+      </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -8291,73 +8286,73 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
 (MATH)</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -8374,34 +8369,34 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
+          <t>Swathi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
           <t>Bhavani
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>Maheswari
+(COMP)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Lalitha
@@ -8422,20 +8417,20 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
+          <t>Bheema
+(PHY)</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8442,7 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -8464,8 +8459,8 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Sai Lakshmi
+(EVS)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -8476,43 +8471,44 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Swathi
+(TEL)</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N30" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8520,7 @@
       <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -8602,27 +8598,27 @@
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (ENG)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
       <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Tulasi
@@ -8631,44 +8627,44 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(BIO)</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8760,7 @@
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -8776,13 +8772,13 @@
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Naga mani
-(TEL)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -8800,13 +8796,13 @@
       <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Maha
-(ENG)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(G.K)</t>
+          <t>Lalitha
+(CHEM)</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -8818,19 +8814,19 @@
       <c r="L34" s="7" t="inlineStr">
         <is>
           <t>Fathima
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
           <t>Bheema
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>Riya
-(HIN)</t>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -8842,45 +8838,45 @@
       <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
 (HIN)</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(G.K)</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Ravi
@@ -8889,8 +8885,8 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>Lalitha
+(BIO)</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -8901,14 +8897,14 @@
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
           <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -8919,8 +8915,8 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(MATH)</t>
+          <t>Naga mani
+(TEL)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -8937,8 +8933,8 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -8949,16 +8945,16 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
@@ -8967,8 +8963,8 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Fathima
+(HIN)</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -8979,14 +8975,14 @@
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -8997,26 +8993,26 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -9033,32 +9029,32 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(G.K)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(PHY)</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>Ravi
 (GRAM)</t>
         </is>
       </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
       <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
         <is>
           <t>Bheema
 (CHEM)</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
@@ -9081,50 +9077,50 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Bhavani
+(MATH)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
 (EVS)</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(G.K)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -9133,10 +9129,9 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
+      <c r="M38" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
@@ -9154,55 +9149,55 @@
       <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Swathi
+(TEL)</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Fathima
+(HIN)</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
           <t>Ravi
-(ENG)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -9230,14 +9225,14 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Sitha
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
 (EVS)</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -9248,44 +9243,44 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
           <t>Lalitha
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -9294,9 +9289,10 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="N40" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -9373,10 +9369,9 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
+      <c r="N41" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9392,31 +9387,31 @@
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (EVS)</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(G.K)</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Swathi
+(TEL)</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -9433,8 +9428,8 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Lalitha
+(PHY)</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
@@ -9451,14 +9446,14 @@
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="inlineStr">
-        <is>
           <t>Sunitha
 (SOC)</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9465,7 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -9481,8 +9476,8 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Maha
+(ENG)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -9493,8 +9488,8 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Maha
-(ENG)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -9505,14 +9500,14 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
           <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
@@ -9523,20 +9518,20 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>Bheema
-(PHY)</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="inlineStr">
-        <is>
           <t>Sunitha
 (SOC)</t>
         </is>
       </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>Gowtham
-(MATH)</t>
+          <t>Bheema
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -9553,58 +9548,58 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Swathi
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (HIN)</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
       <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(BIO)</t>
-        </is>
-      </c>
       <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
-        </is>
-      </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
           <t>Gowtham
@@ -9613,8 +9608,8 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Riya
-(HIN)</t>
+          <t>Bheema
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -9625,16 +9620,16 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(EVS)</t>
-        </is>
-      </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Maheswari
@@ -9655,44 +9650,44 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
       <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>Bheema
 (CHEM)</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -9703,8 +9698,8 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(EVS)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -9716,55 +9711,55 @@
       <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(CHEM)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>Chalapathi
 (BIO)</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
       <c r="N46" s="12" t="inlineStr">
@@ -9781,37 +9776,37 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Fathima
+(HIN)</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -9828,8 +9823,8 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(PHY)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -9838,15 +9833,16 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -9858,73 +9854,73 @@
       <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(HIN)</t>
+        </is>
+      </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(GRAM)</t>
-        </is>
-      </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(TEL)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="inlineStr">
         <is>
           <t>Chalapathi
 (BIO)</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
     </row>

--- a/NRCS/Output/NRCS_Timetable_Final.xlsx
+++ b/NRCS/Output/NRCS_Timetable_Final.xlsx
@@ -659,21 +659,25 @@
       <c r="C5" s="7" t="inlineStr"/>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -691,24 +695,28 @@
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
+      <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -726,24 +734,28 @@
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -758,27 +770,31 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr"/>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -793,29 +809,25 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>U.K.G (EVS)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 2 (G.K)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
+      <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (EVS)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -832,35 +844,23 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -940,7 +940,7 @@
       <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (PHY)</t>
+          <t>Class 10 (PHY)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
@@ -954,11 +954,15 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="inlineStr"/>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -980,11 +984,19 @@
       <c r="B16" s="7" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr"/>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
       <c r="H16" s="7" t="inlineStr"/>
@@ -996,22 +1008,14 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
+      <c r="B17" s="7" t="inlineStr"/>
       <c r="C17" s="7" t="inlineStr"/>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (PHY)</t>
-        </is>
-      </c>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
@@ -1023,18 +1027,18 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr"/>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="7" t="inlineStr"/>
       <c r="G18" s="7" t="inlineStr"/>
       <c r="H18" s="7" t="inlineStr"/>
@@ -1054,14 +1058,10 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="7" t="inlineStr"/>
@@ -1140,8 +1140,16 @@
       <c r="D23" s="7" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr"/>
       <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1155,12 +1163,12 @@
       <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1175,17 +1183,13 @@
       <c r="E25" s="7" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr"/>
@@ -1200,13 +1204,13 @@
       <c r="C26" s="7" t="inlineStr"/>
       <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
+      <c r="H26" s="7" t="inlineStr"/>
       <c r="I26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1220,10 +1224,14 @@
       <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (BIO)</t>
+          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr"/>
@@ -1238,14 +1246,10 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Class 8 (BIO)</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -1323,24 +1327,24 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr"/>
-      <c r="C32" s="7" t="inlineStr"/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
+      <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
+      <c r="G32" s="7" t="inlineStr"/>
       <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
@@ -1358,29 +1362,29 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr"/>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1395,14 +1399,10 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
+      <c r="C34" s="7" t="inlineStr"/>
       <c r="D34" s="7" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
@@ -1414,7 +1414,11 @@
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr">
         <is>
@@ -1431,15 +1435,15 @@
       <c r="B35" s="7" t="inlineStr"/>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr"/>
       <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
@@ -1448,7 +1452,7 @@
       <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -1463,29 +1467,29 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr"/>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
+      <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1498,29 +1502,29 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr"/>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
       <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
+      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1603,23 +1607,23 @@
       <c r="C41" s="7" t="inlineStr"/>
       <c r="D41" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
@@ -1642,23 +1646,23 @@
       <c r="C42" s="7" t="inlineStr"/>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (G.K)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr"/>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -1680,26 +1684,26 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr"/>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1719,22 +1723,22 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
       <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="7" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
       <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
+      <c r="H44" s="7" t="inlineStr"/>
       <c r="I44" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1755,18 +1759,18 @@
       <c r="C45" s="7" t="inlineStr"/>
       <c r="D45" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr"/>
@@ -1790,12 +1794,12 @@
       <c r="C46" s="7" t="inlineStr"/>
       <c r="D46" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
@@ -1882,19 +1886,15 @@
       <c r="B50" s="7" t="inlineStr"/>
       <c r="C50" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
-        </is>
-      </c>
+      <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr"/>
       <c r="H50" s="7" t="inlineStr"/>
@@ -1912,7 +1912,11 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
@@ -1928,19 +1932,15 @@
       <c r="B52" s="7" t="inlineStr"/>
       <c r="C52" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (MATH)</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
-        </is>
-      </c>
+      <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr"/>
       <c r="G52" s="7" t="inlineStr"/>
       <c r="H52" s="7" t="inlineStr"/>
@@ -1953,17 +1953,17 @@
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr"/>
-      <c r="C53" s="7" t="inlineStr"/>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr"/>
@@ -1978,19 +1978,15 @@
       <c r="B54" s="7" t="inlineStr"/>
       <c r="C54" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
-        </is>
-      </c>
+      <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr"/>
       <c r="G54" s="7" t="inlineStr"/>
       <c r="H54" s="7" t="inlineStr"/>
@@ -2003,18 +1999,22 @@
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr"/>
-      <c r="C55" s="7" t="inlineStr"/>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (MATH)</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr"/>
       <c r="G55" s="7" t="inlineStr"/>
       <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
@@ -2087,7 +2087,11 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
@@ -2095,23 +2099,23 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr"/>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr"/>
@@ -2124,33 +2128,33 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr"/>
@@ -2161,31 +2165,35 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (BIO)</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr"/>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr"/>
@@ -2199,7 +2207,7 @@
       <c r="B62" s="7" t="inlineStr"/>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -2216,7 +2224,7 @@
       <c r="G62" s="7" t="inlineStr"/>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr"/>
@@ -2227,11 +2235,7 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
+      <c r="B63" s="7" t="inlineStr"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Class 7 (BIO)</t>
@@ -2239,23 +2243,23 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr"/>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr"/>
@@ -2266,35 +2270,31 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
+      <c r="B64" s="7" t="inlineStr"/>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
@@ -2374,28 +2374,28 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (GRAM)</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (GRAM)</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
@@ -2417,28 +2417,28 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (GRAM)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
+          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr"/>
@@ -2476,12 +2476,12 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
+          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
@@ -2501,26 +2501,26 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
+          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
@@ -2537,33 +2537,33 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (GRAM)</t>
+          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (GRAM)</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -2590,23 +2590,23 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (GRAM)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
+          <t>Class 5 (GRAM)</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -2685,21 +2685,13 @@
       </c>
       <c r="B77" s="7" t="inlineStr"/>
       <c r="C77" s="7" t="inlineStr"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (COMP)</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="inlineStr"/>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
+      <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="7" t="inlineStr"/>
@@ -2713,12 +2705,12 @@
       <c r="B78" s="7" t="inlineStr"/>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (COMP)</t>
+          <t>Class 6 (COMP)</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
+          <t>Class 1 (COMP)</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr"/>
@@ -2737,10 +2729,14 @@
       <c r="C79" s="7" t="inlineStr"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr"/>
       <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr"/>
@@ -2754,10 +2750,14 @@
       </c>
       <c r="B80" s="7" t="inlineStr"/>
       <c r="C80" s="7" t="inlineStr"/>
-      <c r="D80" s="7" t="inlineStr"/>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
+          <t>Class 4 (COMP)</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
@@ -2772,14 +2772,18 @@
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr"/>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr"/>
+      <c r="D81" s="7" t="inlineStr"/>
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>Class 1 (COMP)</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
@@ -2791,11 +2795,7 @@
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr"/>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
+      <c r="C82" s="7" t="inlineStr"/>
       <c r="D82" s="7" t="inlineStr"/>
       <c r="E82" s="7" t="inlineStr">
         <is>
@@ -2880,23 +2880,23 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr"/>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr"/>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
+      <c r="G86" s="7" t="inlineStr"/>
       <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr">
         <is>
@@ -2915,28 +2915,20 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr"/>
+      <c r="C87" s="7" t="inlineStr"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
+      <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
+      <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -2957,20 +2949,20 @@
       <c r="C88" s="7" t="inlineStr"/>
       <c r="D88" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
+      <c r="G88" s="7" t="inlineStr"/>
       <c r="H88" s="7" t="inlineStr"/>
       <c r="I88" s="8" t="inlineStr">
         <is>
@@ -3021,24 +3013,24 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (G.K)</t>
+          <t>Class 1 (TEL)</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr"/>
       <c r="D90" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (TEL)</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (TEL)</t>
+          <t>Class 1 (G.K)</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -3060,23 +3052,31 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (TEL)</t>
+          <t>Class 1 (G.K)</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (TEL)</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3164,20 +3164,20 @@
       <c r="D95" s="7" t="inlineStr"/>
       <c r="E95" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3195,28 +3195,28 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr"/>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr"/>
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr"/>
       <c r="G96" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
+      <c r="H96" s="7" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3229,31 +3229,31 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr"/>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr"/>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
@@ -3278,21 +3278,21 @@
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr"/>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
+      <c r="E98" s="7" t="inlineStr"/>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -3312,26 +3312,26 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr"/>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr"/>
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr"/>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
@@ -3353,13 +3353,13 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr"/>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
@@ -3367,12 +3367,12 @@
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G100" s="7" t="inlineStr"/>
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3450,21 +3450,21 @@
       <c r="B104" s="7" t="inlineStr"/>
       <c r="C104" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
       <c r="E104" s="7" t="inlineStr"/>
-      <c r="F104" s="7" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr">
         <is>
           <t>Class 9 (GRAM)</t>
         </is>
       </c>
-      <c r="G104" s="7" t="inlineStr"/>
       <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="7" t="inlineStr"/>
     </row>
@@ -3475,24 +3475,24 @@
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr"/>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (GRAM)</t>
-        </is>
-      </c>
+      <c r="F105" s="7" t="inlineStr"/>
       <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (GRAM)</t>
+        </is>
+      </c>
       <c r="I105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3502,24 +3502,24 @@
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr"/>
-      <c r="C106" s="7" t="inlineStr"/>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr"/>
+      <c r="E106" s="7" t="inlineStr"/>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (GRAM)</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (GRAM)</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
@@ -3529,18 +3529,18 @@
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr"/>
-      <c r="C107" s="7" t="inlineStr"/>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
       <c r="D107" s="7" t="inlineStr"/>
       <c r="E107" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
+      <c r="F107" s="7" t="inlineStr"/>
       <c r="G107" s="7" t="inlineStr"/>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
@@ -3552,25 +3552,21 @@
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr"/>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr"/>
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr"/>
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>Class 6 (GRAM)</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (GRAM)</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr"/>
@@ -3583,20 +3579,24 @@
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr"/>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr"/>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr"/>
-      <c r="E109" s="7" t="inlineStr"/>
-      <c r="F109" s="7" t="inlineStr"/>
-      <c r="G109" s="7" t="inlineStr"/>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+      <c r="H109" s="7" t="inlineStr"/>
       <c r="I109" s="7" t="inlineStr"/>
     </row>
     <row r="111">
@@ -3667,18 +3667,22 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr"/>
+      <c r="C113" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr"/>
-      <c r="E113" s="7" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr"/>
       <c r="G113" s="7" t="inlineStr"/>
       <c r="H113" s="7" t="inlineStr"/>
@@ -3691,14 +3695,10 @@
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr"/>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr"/>
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="D114" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
@@ -3718,17 +3718,17 @@
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr"/>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr"/>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr"/>
       <c r="G115" s="7" t="inlineStr"/>
       <c r="H115" s="7" t="inlineStr"/>
@@ -3740,22 +3740,18 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr"/>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
+      <c r="D116" s="7" t="inlineStr"/>
+      <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr"/>
       <c r="G116" s="7" t="inlineStr"/>
       <c r="H116" s="7" t="inlineStr"/>
@@ -3768,15 +3764,19 @@
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr"/>
-      <c r="C117" s="7" t="inlineStr"/>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
@@ -3790,20 +3790,20 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr"/>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr"/>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
@@ -3886,26 +3886,30 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="D122" s="7" t="inlineStr"/>
-      <c r="E122" s="7" t="inlineStr">
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr"/>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
         <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="H122" s="7" t="inlineStr"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3925,28 +3929,28 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="I123" s="8" t="inlineStr">
@@ -3963,17 +3967,17 @@
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr"/>
@@ -3984,12 +3988,12 @@
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (G.K)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="I124" s="8" t="inlineStr">
@@ -4014,25 +4018,21 @@
           <t>Class 1 (EVS)</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr"/>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr">
         <is>
           <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr"/>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H125" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="I125" s="8" t="inlineStr">
@@ -4054,28 +4054,28 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="I126" s="8" t="inlineStr">
@@ -4102,23 +4102,23 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>Class 1 (EVS)</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="I127" s="8" t="inlineStr">
@@ -4202,30 +4202,26 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (G.K)</t>
-        </is>
-      </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr"/>
+      <c r="D131" s="7" t="inlineStr"/>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="H131" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (COMP)</t>
-        </is>
-      </c>
+          <t>Class 4 (G.K)</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4238,33 +4234,25 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
+      <c r="B132" s="7" t="inlineStr"/>
+      <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="7" t="inlineStr"/>
       <c r="E132" s="7" t="inlineStr">
         <is>
           <t>Class 5 (G.K)</t>
         </is>
       </c>
-      <c r="F132" s="7" t="inlineStr">
+      <c r="F132" s="7" t="inlineStr"/>
+      <c r="G132" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="G132" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="H132" s="7" t="inlineStr"/>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4279,7 +4267,7 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 6 (G.K)</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
@@ -4287,17 +4275,17 @@
           <t>Class 7 (COMP)</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr"/>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="D133" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
+      <c r="E133" s="7" t="inlineStr"/>
       <c r="F133" s="7" t="inlineStr"/>
       <c r="G133" s="7" t="inlineStr"/>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="I133" s="8" t="inlineStr">
@@ -4317,20 +4305,24 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="C134" s="7" t="inlineStr"/>
+      <c r="D134" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr"/>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (MATH)</t>
+          <t>Class 8 (COMP)</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
       <c r="G134" s="7" t="inlineStr"/>
-      <c r="H134" s="7" t="inlineStr"/>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4343,29 +4335,33 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B135" s="7" t="inlineStr"/>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (G.K)</t>
-        </is>
-      </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
           <t>Class 6 (MATH)</t>
         </is>
       </c>
+      <c r="D135" s="7" t="inlineStr"/>
       <c r="E135" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="F135" s="7" t="inlineStr"/>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="H135" s="7" t="inlineStr"/>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr"/>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="I135" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4378,24 +4374,28 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B136" s="7" t="inlineStr"/>
-      <c r="C136" s="7" t="inlineStr"/>
-      <c r="D136" s="7" t="inlineStr">
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr"/>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="inlineStr"/>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
+      <c r="G136" s="7" t="inlineStr"/>
       <c r="H136" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
@@ -4477,33 +4477,29 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr"/>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr"/>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="C140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr"/>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="I140" s="8" t="inlineStr">
@@ -4523,15 +4519,19 @@
           <t>L.K.G (ORAL)</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr"/>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
@@ -4559,30 +4559,26 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr"/>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr"/>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
+      <c r="G142" s="7" t="inlineStr"/>
       <c r="H142" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
@@ -4607,23 +4603,23 @@
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
@@ -4645,31 +4641,35 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C144" s="7" t="inlineStr">
+      <c r="D144" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr"/>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
+      <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (EVS)</t>
         </is>
       </c>
-      <c r="G144" s="7" t="inlineStr">
+      <c r="H144" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ENG)</t>
         </is>
       </c>
-      <c r="H144" s="7" t="inlineStr"/>
       <c r="I144" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4684,28 +4684,28 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr"/>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
+      <c r="G145" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F145" s="7" t="inlineStr"/>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
@@ -4793,17 +4793,17 @@
       <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
         </is>
       </c>
       <c r="I149" s="7" t="inlineStr"/>
@@ -4820,20 +4820,20 @@
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr"/>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G150" s="7" t="inlineStr">
+      <c r="I150" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="H150" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="I150" s="7" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -4847,20 +4847,20 @@
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr"/>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
+      <c r="I151" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="I151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -4901,20 +4901,20 @@
       <c r="E153" s="7" t="inlineStr"/>
       <c r="F153" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr"/>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
+      <c r="I153" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="I153" s="7" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -4926,17 +4926,17 @@
       <c r="C154" s="7" t="inlineStr"/>
       <c r="D154" s="7" t="inlineStr"/>
       <c r="E154" s="7" t="inlineStr"/>
-      <c r="F154" s="7" t="inlineStr">
+      <c r="F154" s="7" t="inlineStr"/>
+      <c r="G154" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G154" s="7" t="inlineStr">
+      <c r="H154" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="H154" s="7" t="inlineStr"/>
       <c r="I154" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
@@ -5013,20 +5013,20 @@
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr"/>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="C158" s="7" t="inlineStr">
+      <c r="E158" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="D158" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="inlineStr"/>
       <c r="F158" s="7" t="inlineStr"/>
       <c r="G158" s="7" t="inlineStr"/>
       <c r="H158" s="7" t="inlineStr"/>
@@ -5048,12 +5048,12 @@
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="D159" s="7" t="inlineStr">
+      <c r="D159" s="7" t="inlineStr"/>
+      <c r="E159" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="7" t="inlineStr"/>
       <c r="G159" s="7" t="inlineStr"/>
       <c r="H159" s="7" t="inlineStr"/>
@@ -5067,18 +5067,18 @@
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr"/>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="inlineStr"/>
-      <c r="D160" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
@@ -5094,18 +5094,18 @@
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr"/>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="C161" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="D161" s="7" t="inlineStr"/>
-      <c r="E161" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
@@ -5126,15 +5126,15 @@
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr"/>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="D162" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="7" t="inlineStr"/>
       <c r="G162" s="7" t="inlineStr"/>
       <c r="H162" s="7" t="inlineStr"/>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
@@ -5159,7 +5159,7 @@
       <c r="D163" s="7" t="inlineStr"/>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
@@ -5242,26 +5242,22 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (HIN)</t>
+          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr"/>
       <c r="E167" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
       <c r="G167" s="7" t="inlineStr"/>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
+      <c r="H167" s="7" t="inlineStr"/>
       <c r="I167" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5279,28 +5275,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C168" s="7" t="inlineStr"/>
-      <c r="D168" s="7" t="inlineStr">
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr"/>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr"/>
       <c r="G168" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
+      <c r="H168" s="7" t="inlineStr"/>
       <c r="I168" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5321,23 +5317,23 @@
       <c r="C169" s="7" t="inlineStr"/>
       <c r="D169" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr"/>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr"/>
-      <c r="H169" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="I169" s="8" t="inlineStr">
@@ -5357,26 +5353,26 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C170" s="7" t="inlineStr"/>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr"/>
+      <c r="F170" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr"/>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
+          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="I170" s="8" t="inlineStr">
@@ -5396,28 +5392,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C171" s="7" t="inlineStr"/>
-      <c r="D171" s="7" t="inlineStr">
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr"/>
+      <c r="E171" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="E171" s="7" t="inlineStr">
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr"/>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
+      <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5437,11 +5433,15 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr"/>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D172" s="7" t="inlineStr"/>
-      <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
+          <t>U.K.G (HIN)</t>
         </is>
       </c>
       <c r="H172" s="7" t="inlineStr"/>
@@ -5527,20 +5527,20 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B176" s="7" t="inlineStr">
+      <c r="B176" s="7" t="inlineStr"/>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
         <is>
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C176" s="7" t="inlineStr">
+      <c r="E176" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="D176" s="7" t="inlineStr"/>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="I176" s="8" t="inlineStr">
@@ -5566,10 +5566,14 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B177" s="7" t="inlineStr"/>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr"/>
@@ -5580,15 +5584,15 @@
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="inlineStr"/>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr"/>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5608,26 +5612,22 @@
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr"/>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="G178" s="7" t="inlineStr"/>
-      <c r="H178" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr"/>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5650,23 +5650,19 @@
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr"/>
+      <c r="D179" s="7" t="inlineStr"/>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr"/>
-      <c r="H179" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
+      <c r="H179" s="7" t="inlineStr"/>
       <c r="I179" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5684,26 +5680,26 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
+      <c r="C180" s="7" t="inlineStr"/>
       <c r="D180" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="E180" s="7" t="inlineStr"/>
       <c r="F180" s="7" t="inlineStr"/>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="I180" s="8" t="inlineStr">
@@ -5726,21 +5722,25 @@
       <c r="C181" s="7" t="inlineStr"/>
       <c r="D181" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr"/>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="inlineStr"/>
-      <c r="H181" s="7" t="inlineStr"/>
       <c r="I181" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5821,17 +5821,17 @@
       <c r="E185" s="7" t="inlineStr"/>
       <c r="F185" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (P.E.T)</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (P.E.T)</t>
         </is>
       </c>
-      <c r="G185" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (P.E.T)</t>
-        </is>
-      </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (P.E.T)</t>
+          <t>Class 1 (P.E.T)</t>
         </is>
       </c>
       <c r="I185" s="7" t="inlineStr"/>
@@ -5848,17 +5848,17 @@
       <c r="E186" s="7" t="inlineStr"/>
       <c r="F186" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (P.E.T)</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (P.E.T)</t>
         </is>
       </c>
-      <c r="G186" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (P.E.T)</t>
-        </is>
-      </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (P.E.T)</t>
+          <t>Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="I186" s="7" t="inlineStr"/>
@@ -5875,15 +5875,19 @@
       <c r="E187" s="7" t="inlineStr"/>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H187" s="7" t="inlineStr"/>
+          <t>Class 8 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I187" s="7" t="inlineStr"/>
     </row>
     <row r="188">
@@ -5898,11 +5902,15 @@
       <c r="E188" s="7" t="inlineStr"/>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (P.E.T)</t>
+          <t>Class 6 (P.E.T)</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr"/>
-      <c r="H188" s="7" t="inlineStr"/>
+      <c r="H188" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I188" s="7" t="inlineStr"/>
     </row>
     <row r="189">
@@ -5917,13 +5925,13 @@
       <c r="E189" s="7" t="inlineStr"/>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
+          <t>Class 2 (P.E.T)</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr"/>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (P.E.T)</t>
+          <t>Class 9 (P.E.T)</t>
         </is>
       </c>
       <c r="I189" s="7" t="inlineStr"/>
@@ -5940,13 +5948,13 @@
       <c r="E190" s="7" t="inlineStr"/>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr"/>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (P.E.T)</t>
+          <t>U.K.G (P.E.T)</t>
         </is>
       </c>
       <c r="I190" s="7" t="inlineStr"/>
@@ -6246,7 +6254,7 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -6275,8 +6283,8 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>Lalitha
+(EVS)</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -6305,14 +6313,14 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -6323,28 +6331,28 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Sitha
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (ENG)</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(HIN)</t>
-        </is>
-      </c>
       <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Lalitha
@@ -6359,38 +6367,38 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>Swathi
+(TEL)</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(G.K)</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>Ravi
 (ENG)</t>
         </is>
       </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>Sunitha
-(SOC)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N3" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -6407,68 +6415,68 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>Sai Lakshmi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>Bhavani
 (MATH)</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Maha
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Maheswari
-(COMP)</t>
+          <t>Riya
+(HIN)</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
+(BIO)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>Ravi
 (ENG)</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
       <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -6479,74 +6487,74 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Maheswari
 (COMP)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
       <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
 (SOC)</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Riya
 (HIN)</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(PHY)</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Bheema
 (PHY)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -6557,68 +6565,68 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
@@ -6635,19 +6643,19 @@
       <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (ENG)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(EVS)</t>
+          <t>Bhavani
+(MATH)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -6664,8 +6672,8 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Sangeetha
+(G.K)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -6676,26 +6684,26 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Lalitha
+(PHY)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Ravi
+(GRAM)</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -6713,67 +6721,67 @@
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
 (MATH)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
       <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(CHEM)</t>
-        </is>
-      </c>
       <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(COMP)</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -6903,8 +6911,8 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -6915,8 +6923,8 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Lalitha
+(BIO)</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -6933,8 +6941,8 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Bheema
+(CHEM)</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -6951,62 +6959,62 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Sitha
+(EVS)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
+          <t>Bhavani
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Maheswari
 (COMP)</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -7030,73 +7038,73 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(EVS)</t>
+          <t>Naga mani
+(TEL)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Maha
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
       <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>Bheema
 (CHEM)</t>
         </is>
       </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>Riya
-(HIN)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7116,7 @@
       <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -7137,8 +7145,8 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -7149,20 +7157,20 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
           <t>Ravi
 (ENG)</t>
         </is>
       </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(G.K)</t>
+        </is>
+      </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Sunitha
+(SOC)</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -7191,68 +7199,66 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Naga mani
-(TEL)</t>
+          <t>Sai Lakshmi
+(ENG)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(BIO)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(G.K)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7269,34 +7275,34 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
+          <t>Bhavani
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Pallavi
@@ -7312,7 +7318,7 @@
       <c r="K15" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -7323,14 +7329,14 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Sonu
-(ENG)</t>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -7342,73 +7348,72 @@
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
 (MATH)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(TEL)</t>
+          <t>Lalitha
+(EVS)</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(BIO)</t>
-        </is>
-      </c>
       <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
+      <c r="N16" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7485,9 +7490,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N17" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7509,7 @@
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -7521,7 +7527,7 @@
       <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -7545,13 +7551,13 @@
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
-(MATH)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Lalitha
+(PHY)</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -7562,14 +7568,14 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -7581,49 +7587,49 @@
       <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
+          <t>Sai Lakshmi
+(ENG)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Riya
-(HIN)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(BIO)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -7634,20 +7640,20 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
           <t>Bheema
-(PHY)</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -7658,46 +7664,46 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(HIN)</t>
+        </is>
+      </c>
       <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
 (EVS)</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Maheswari
 (COMP)</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Pallavi
@@ -7706,26 +7712,26 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>Sunitha
-(SOC)</t>
+          <t>Bheema
+(CHEM)</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -7736,16 +7742,16 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(HIN)</t>
-        </is>
-      </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Bhavani
@@ -7754,40 +7760,40 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
@@ -7796,14 +7802,14 @@
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
+          <t>Bheema
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -7826,38 +7832,38 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Lalitha
+(EVS)</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(TEL)</t>
+          <t>Fathima
+(HIN)</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -7868,20 +7874,20 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
+          <t>Sonu
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>Chalapathi
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
           <t>Ravi
 (GRAM)</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -7892,68 +7898,68 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
+          <t>Sai Lakshmi
+(HIN)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
       <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(BIO)</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(PHY)</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
-        </is>
-      </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>Chalapathi
-(BIO)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
@@ -7975,67 +7981,68 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
       <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>Lalitha
+(CHEM)</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Sangeetha
 (MATH)</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>Chalapathi
 (BIO)</t>
-        </is>
-      </c>
-      <c r="M24" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -8112,9 +8119,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N25" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8144,7 @@
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -8189,14 +8197,14 @@
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8216,7 @@
       <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -8237,44 +8245,44 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Maha
-(ENG)</t>
+          <t>Lalitha
+(EVS)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(CHEM)</t>
-        </is>
-      </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Gowtham
 (MATH)</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -8286,27 +8294,27 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Lalitha
@@ -8315,44 +8323,44 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
           <t>Bheema
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -8369,34 +8377,34 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
           <t>Bhavani
 (MATH)</t>
         </is>
       </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
       <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Maheswari
 (COMP)</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Lalitha
@@ -8411,26 +8419,25 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
           <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
+(COMP)</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>Sunitha
 (SOC)</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8442,55 +8449,55 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (EVS)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
       <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>Fathima
+(HIN)</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -8507,8 +8514,8 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Chalapathi
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -8520,13 +8527,13 @@
       <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
 (MATH)</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(ENG)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -8603,68 +8610,68 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
       <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>Fathima
-(HIN)</t>
+          <t>Lalitha
+(BIO)</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -8760,19 +8767,19 @@
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
 (EVS)</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Naga mani
-(G.K)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -8796,13 +8803,13 @@
       <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Maha
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(CHEM)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -8819,8 +8826,8 @@
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>Bheema
-(PHY)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
@@ -8838,49 +8845,49 @@
       <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Sitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
 (ENG)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
       <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(G.K)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
           <t>Sangeetha
-(G.K)</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
 (MATH)</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
@@ -8891,20 +8898,20 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
           <t>Sunitha
 (SOC)</t>
         </is>
       </c>
-      <c r="N35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -8915,74 +8922,74 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
       <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>Sunitha
-(SOC)</t>
+          <t>Bheema
+(PHY)</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -8993,74 +9000,74 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(G.K)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
         <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -9072,13 +9079,13 @@
       <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
+          <t>Sai Lakshmi
+(ENG)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -9089,55 +9096,55 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Maheswari
+(COMP)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr">
+      <c r="N38" s="12" t="inlineStr">
         <is>
           <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9149,72 +9156,72 @@
       <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
+          <t>Swathi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
           <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
+(G.K)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>Sai Lakshmi
 (HIN)</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Lalitha
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
+(PHY)</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Chalapathi
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N39" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9225,74 +9232,74 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Maha
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Naga mani
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>Tulasi
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>Swathi
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>Lalitha
-(PHY)</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>Chalapathi
 (BIO)</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>Sonu
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -9369,9 +9376,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N41" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -9387,19 +9395,19 @@
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Bhavani
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
           <t>Naga mani
-(TEL)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -9428,8 +9436,8 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(PHY)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
@@ -9446,14 +9454,14 @@
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
+          <t>D.V.Rao
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
           <t>Sunitha
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="inlineStr">
-        <is>
-          <t>Riya
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9473,7 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -9488,32 +9496,32 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
           <t>Pallavi
 (SOC)</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Swathi
 (TEL)</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Maheswari
-(COMP)</t>
-        </is>
-      </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
           <t>Lalitha
-(BIO)</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>Ravi
-(ENG)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -9524,8 +9532,8 @@
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>Riya
-(HIN)</t>
+          <t>Gowtham
+(MATH)</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
@@ -9543,73 +9551,73 @@
       <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>Tulasi
 (MATH)</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Fathima
 (HIN)</t>
         </is>
       </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(ENG)</t>
+        </is>
+      </c>
       <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
         </is>
       </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>Bheema
+(PHY)</t>
+        </is>
+      </c>
       <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>Riya
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
         <is>
           <t>Gowtham
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(PHY)</t>
         </is>
       </c>
     </row>
@@ -9620,16 +9628,16 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Sitha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
           <t>Naga mani
 (TEL)</t>
         </is>
       </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Bhavani
+(MATH)</t>
+        </is>
+      </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Maheswari
@@ -9644,50 +9652,50 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
+          <t>Pallavi
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Swathi
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Lalitha
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>Fathima
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>Ravi
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>Sangeetha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>Sunitha
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
           <t>Riya
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Pallavi
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>Fathima
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>Sangeetha
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>Bheema
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>Gowtham
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
-        <is>
-          <t>Sunitha
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9698,22 +9706,22 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
+          <t>Sitha
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Sai Lakshmi
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
           <t>P.E
@@ -9722,14 +9730,14 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Tulasi
-(MATH)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
           <t>Maha
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -9746,25 +9754,26 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(BIO)</t>
+          <t>Sangeetha
+(MATH)</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>Chalapathi
-(BIO)</t>
+          <t>D.V.Rao
+(TEL)</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>Sonu
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N46" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+          <t>Gowtham
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -9776,31 +9785,31 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>Sitha
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(EVS)</t>
+          <t>Swathi
+(HIN)</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
           <t>Sai Lakshmi
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>Maha
-(ENG)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Lalitha
-(EVS)</t>
+          <t>Tulasi
+(MATH)</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -9811,38 +9820,38 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Swathi
-(TEL)</t>
+          <t>Maha
+(GRAM)</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>Pallavi
-(SOC)</t>
+          <t>Lalitha
+(CHEM)</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Sangeetha
-(MATH)</t>
+          <t>Ravi
+(ENG)</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>Chalapathi
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>Sonu
 (ENG)</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr">
+      <c r="N47" s="7" t="inlineStr">
         <is>
           <t>D.V.Rao
 (TEL)</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>Chalapathi
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -9865,38 +9874,38 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Bhavani
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
           <t>Sai Lakshmi
 (HIN)</t>
         </is>
       </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Naga mani
+(TEL)</t>
+        </is>
+      </c>
       <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>Maha
 (ENG)</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>Lalitha
 (EVS)</t>
         </is>
       </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>Tulasi
+(MATH)</t>
+        </is>
+      </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>Ravi
-(ENG)</t>
+          <t>Pallavi
+(SOC)</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
@@ -9907,8 +9916,8 @@
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>Sonu
+(ENG)</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -9917,10 +9926,9 @@
 (BIO)</t>
         </is>
       </c>
-      <c r="N48" s="7" t="inlineStr">
-        <is>
-          <t>D.V.Rao
-(TEL)</t>
+      <c r="N48" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>

--- a/NRCS/Output/NRCS_Timetable_Final.xlsx
+++ b/NRCS/Output/NRCS_Timetable_Final.xlsx
@@ -673,7 +673,11 @@
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -691,24 +695,28 @@
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>U.K.G (EVS)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -731,23 +739,15 @@
           <t>Class 1 (MATH)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (EVS)</t>
-        </is>
-      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
+      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -765,24 +765,24 @@
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (MATH)</t>
-        </is>
-      </c>
+      <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="8" t="inlineStr">
         <is>
           <t>U.K.G</t>
@@ -800,15 +800,15 @@
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (MATH)</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -819,7 +819,7 @@
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (MATH)</t>
+          <t>U.K.G (MATH)</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -839,25 +839,25 @@
           <t>U.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Class 2 (G.K)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (MATH)</t>
+          <t>Class 1 (MATH)</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -938,12 +938,12 @@
       <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (PHY)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -958,19 +958,15 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -988,7 +984,7 @@
       <c r="B16" s="7" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 9 (PHY)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -1011,14 +1007,10 @@
       <c r="B17" s="7" t="inlineStr"/>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
@@ -1031,11 +1023,19 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr"/>
-      <c r="C18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       <c r="B19" s="7" t="inlineStr"/>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (PHY)</t>
+          <t>Class 9 (PHY)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -1144,7 +1144,11 @@
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
     </row>
@@ -1158,7 +1162,11 @@
       <c r="C24" s="7" t="inlineStr"/>
       <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="inlineStr"/>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -1177,17 +1185,9 @@
       <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
+      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1202,13 +1202,13 @@
       <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
+          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr"/>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (BIO)</t>
+          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr"/>
@@ -1223,15 +1223,19 @@
       <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr"/>
@@ -1246,14 +1250,10 @@
       <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
+          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr"/>
@@ -1334,22 +1334,22 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1367,24 +1367,24 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr"/>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
+      <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1403,23 +1403,23 @@
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr"/>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
+      <c r="E34" s="7" t="inlineStr"/>
       <c r="F34" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1437,23 +1437,23 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr">
         <is>
@@ -1472,18 +1472,18 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr"/>
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr"/>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
+      <c r="F36" s="7" t="inlineStr"/>
       <c r="G36" s="7" t="inlineStr"/>
       <c r="H36" s="7" t="inlineStr">
         <is>
@@ -1507,24 +1507,24 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr"/>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 9</t>
@@ -1604,24 +1604,24 @@
           <t>Class 8 (G.K)</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr"/>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
+      <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
+      <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1641,26 +1641,22 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr"/>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr"/>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (G.K)</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Class 8</t>
@@ -1683,18 +1679,18 @@
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
+      <c r="D43" s="7" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr"/>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr">
         <is>
@@ -1720,13 +1716,13 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr"/>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -1754,24 +1750,24 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr"/>
-      <c r="F45" s="7" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -1791,22 +1787,26 @@
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr"/>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr"/>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -1888,8 +1888,16 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr"/>
-      <c r="D50" s="7" t="inlineStr"/>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr"/>
@@ -1902,7 +1910,11 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr"/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -1910,7 +1922,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
+          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr"/>
@@ -1951,12 +1963,12 @@
       <c r="B53" s="7" t="inlineStr"/>
       <c r="C53" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr"/>
@@ -1971,19 +1983,11 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr"/>
+      <c r="C54" s="7" t="inlineStr"/>
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr"/>
@@ -1998,19 +2002,15 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr"/>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr"/>
@@ -2100,17 +2100,17 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr"/>
@@ -2125,30 +2125,34 @@
       <c r="B60" s="7" t="inlineStr"/>
       <c r="C60" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Class 6 (BIO)</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2160,30 +2164,30 @@
       <c r="B61" s="7" t="inlineStr"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
+          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr"/>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
+      <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2200,27 +2204,27 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr"/>
@@ -2234,32 +2238,28 @@
       <c r="B63" s="7" t="inlineStr"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr"/>
@@ -2273,30 +2273,30 @@
       <c r="B64" s="7" t="inlineStr"/>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr"/>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr"/>
       <c r="I64" s="7" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (ENG)</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr"/>
@@ -2411,28 +2411,28 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr"/>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
@@ -2448,28 +2448,28 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr"/>
       <c r="E70" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (GRAM)</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (GRAM)</t>
-        </is>
-      </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr"/>
@@ -2488,27 +2488,27 @@
       <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (GRAM)</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr"/>
@@ -2524,30 +2524,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr"/>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (GRAM)</t>
+        </is>
+      </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (ENG)</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (ENG)</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (GRAM)</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (ENG)</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr"/>
@@ -2563,30 +2563,30 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr"/>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (GRAM)</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
           <t>Class 1 (ENG)</t>
         </is>
       </c>
+      <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr"/>
@@ -2661,14 +2661,10 @@
       </c>
       <c r="B77" s="7" t="inlineStr"/>
       <c r="C77" s="7" t="inlineStr"/>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (COMP)</t>
-        </is>
-      </c>
+      <c r="D77" s="7" t="inlineStr"/>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
+          <t>Class 5 (COMP)</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
@@ -2685,13 +2681,13 @@
       <c r="B78" s="7" t="inlineStr"/>
       <c r="C78" s="7" t="inlineStr"/>
       <c r="D78" s="7" t="inlineStr"/>
-      <c r="E78" s="7" t="inlineStr"/>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
       <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
+      <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr"/>
     </row>
@@ -2703,13 +2699,17 @@
       </c>
       <c r="B79" s="7" t="inlineStr"/>
       <c r="C79" s="7" t="inlineStr"/>
-      <c r="D79" s="7" t="inlineStr"/>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr"/>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
       <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr"/>
       <c r="I79" s="7" t="inlineStr"/>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="B80" s="7" t="inlineStr"/>
       <c r="C80" s="7" t="inlineStr"/>
-      <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (COMP)</t>
-        </is>
-      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
       <c r="H80" s="7" t="inlineStr"/>
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr"/>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
+      <c r="C81" s="7" t="inlineStr"/>
       <c r="D81" s="7" t="inlineStr"/>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
+          <t>Class 1 (COMP)</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (COMP)</t>
+        </is>
+      </c>
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
     </row>
@@ -2763,24 +2763,24 @@
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr"/>
-      <c r="C82" s="7" t="inlineStr"/>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (COMP)</t>
+        </is>
+      </c>
       <c r="D82" s="7" t="inlineStr"/>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr"/>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr">
         <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (COMP)</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
       <c r="I82" s="7" t="inlineStr"/>
     </row>
     <row r="84">
@@ -2856,19 +2856,19 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr"/>
+      <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr"/>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr"/>
-      <c r="G86" s="7" t="inlineStr"/>
       <c r="H86" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
@@ -2893,25 +2893,17 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr"/>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (G.K)</t>
-        </is>
-      </c>
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr">
         <is>
@@ -2930,26 +2922,26 @@
           <t>Class 1 (G.K)</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr"/>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
+          <t>Class 1 (TEL)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr"/>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr">
         <is>
           <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="H88" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (TEL)</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
@@ -2969,20 +2961,24 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr"/>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
       <c r="D89" s="7" t="inlineStr"/>
-      <c r="E89" s="7" t="inlineStr"/>
-      <c r="F89" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
+      <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3000,24 +2996,24 @@
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr"/>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr"/>
+      <c r="E90" s="7" t="inlineStr"/>
+      <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>L.K.G (TEL)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
+      <c r="H90" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Class 1</t>
@@ -3032,22 +3028,26 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (G.K)</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (TEL)</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (TEL)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr">
         <is>
           <t>U.K.G (TEL)</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr"/>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (TEL)</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr"/>
       <c r="H91" s="7" t="inlineStr">
         <is>
           <t>Class 2 (TEL)</t>
@@ -3134,15 +3134,15 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr"/>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
+      <c r="E95" s="7" t="inlineStr"/>
       <c r="F95" s="7" t="inlineStr"/>
       <c r="G95" s="7" t="inlineStr">
         <is>
@@ -3173,24 +3173,24 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr"/>
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr"/>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr"/>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -3210,26 +3210,26 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr"/>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr"/>
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
       <c r="G98" s="7" t="inlineStr"/>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="I98" s="8" t="inlineStr">
@@ -3288,28 +3288,28 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr"/>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr"/>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
+      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -3329,24 +3329,24 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr"/>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="G100" s="7" t="inlineStr"/>
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr"/>
-      <c r="F100" s="7" t="inlineStr"/>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
@@ -3424,11 +3424,7 @@
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr"/>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
+      <c r="C104" s="7" t="inlineStr"/>
       <c r="D104" s="7" t="inlineStr">
         <is>
           <t>Class 10 (GRAM)</t>
@@ -3441,7 +3437,11 @@
       </c>
       <c r="F104" s="7" t="inlineStr"/>
       <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
       <c r="I104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
@@ -3451,24 +3451,24 @@
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (GRAM)</t>
-        </is>
-      </c>
+      <c r="C105" s="7" t="inlineStr"/>
       <c r="D105" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr"/>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (GRAM)</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr"/>
-      <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3478,26 +3478,18 @@
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr"/>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr"/>
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (GRAM)</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (GRAM)</t>
-        </is>
-      </c>
+      <c r="F106" s="7" t="inlineStr"/>
       <c r="G106" s="7" t="inlineStr"/>
       <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="7" t="inlineStr"/>
@@ -3520,13 +3512,13 @@
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (GRAM)</t>
+        </is>
+      </c>
       <c r="G107" s="7" t="inlineStr"/>
-      <c r="H107" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (GRAM)</t>
-        </is>
-      </c>
+      <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
@@ -3543,13 +3535,17 @@
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (GRAM)</t>
+        </is>
+      </c>
       <c r="I108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
@@ -3559,19 +3555,23 @@
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr"/>
-      <c r="C109" s="7" t="inlineStr"/>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="D109" s="7" t="inlineStr"/>
       <c r="E109" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (GRAM)</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr"/>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+      <c r="G109" s="7" t="inlineStr"/>
       <c r="H109" s="7" t="inlineStr"/>
       <c r="I109" s="7" t="inlineStr"/>
     </row>
@@ -3644,23 +3644,19 @@
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr"/>
-      <c r="C113" s="7" t="inlineStr"/>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="D113" s="7" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
-      <c r="G113" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
+      <c r="F113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr"/>
       <c r="H113" s="7" t="inlineStr"/>
       <c r="I113" s="7" t="inlineStr"/>
     </row>
@@ -3671,24 +3667,24 @@
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr"/>
-      <c r="C114" s="7" t="inlineStr"/>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="G114" s="7" t="inlineStr"/>
-      <c r="H114" s="7" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr"/>
+      <c r="G114" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
+      <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
@@ -3697,17 +3693,25 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="B115" s="7" t="inlineStr"/>
       <c r="C115" s="7" t="inlineStr"/>
       <c r="D115" s="7" t="inlineStr"/>
-      <c r="E115" s="7" t="inlineStr"/>
-      <c r="F115" s="7" t="inlineStr"/>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="G115" s="7" t="inlineStr"/>
-      <c r="H115" s="7" t="inlineStr"/>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
       <c r="I115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
@@ -3717,24 +3721,24 @@
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr"/>
-      <c r="C116" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
+      <c r="C116" s="7" t="inlineStr"/>
       <c r="D116" s="7" t="inlineStr"/>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="H116" s="7" t="inlineStr"/>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
       <c r="I116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
@@ -3771,11 +3775,7 @@
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr"/>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
+      <c r="C118" s="7" t="inlineStr"/>
       <c r="D118" s="7" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
         <is>
@@ -3862,17 +3862,17 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="D122" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
@@ -3910,25 +3910,25 @@
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (HIN)</t>
         </is>
       </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="F123" s="7" t="inlineStr">
+      <c r="G123" s="7" t="inlineStr"/>
+      <c r="H123" s="7" t="inlineStr">
         <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="G123" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="H123" s="7" t="inlineStr"/>
       <c r="I123" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3948,30 +3948,30 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr"/>
-      <c r="H124" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (HIN)</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr"/>
       <c r="I124" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
@@ -3996,25 +3996,25 @@
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>U.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
           <t>Class 1 (HIN)</t>
         </is>
       </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (EVS)</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr"/>
-      <c r="H125" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
+      <c r="H125" s="7" t="inlineStr"/>
       <c r="I125" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -4034,24 +4034,24 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
           <t>U.K.G (ENG)</t>
         </is>
       </c>
-      <c r="D126" s="7" t="inlineStr">
+      <c r="E126" s="7" t="inlineStr"/>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (EVS)</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr"/>
+      <c r="H126" s="7" t="inlineStr">
         <is>
           <t>Class 1 (HIN)</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr"/>
-      <c r="F126" s="7" t="inlineStr"/>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="I126" s="8" t="inlineStr">
@@ -4073,28 +4073,28 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (HIN)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (G.K)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Class 1 (EVS)</t>
+          <t>U.K.G (ENG)</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr"/>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (ENG)</t>
+          <t>Class 1 (HIN)</t>
         </is>
       </c>
       <c r="I127" s="8" t="inlineStr">
@@ -4179,16 +4179,24 @@
       <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="F131" s="7" t="inlineStr"/>
-      <c r="G131" s="7" t="inlineStr"/>
+          <t>Class 4 (G.K)</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (COMP)</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
       <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
@@ -4207,23 +4215,23 @@
           <t>Class 6 (G.K)</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr">
+      <c r="C132" s="7" t="inlineStr"/>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr"/>
+      <c r="G132" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr"/>
-      <c r="F132" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="G132" s="7" t="inlineStr"/>
       <c r="H132" s="7" t="inlineStr"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
@@ -4250,18 +4258,14 @@
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (COMP)</t>
+          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr"/>
-      <c r="G133" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (COMP)</t>
-        </is>
-      </c>
+      <c r="G133" s="7" t="inlineStr"/>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="I133" s="8" t="inlineStr">
@@ -4281,22 +4285,18 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="C134" s="7" t="inlineStr"/>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr"/>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
+      <c r="F134" s="7" t="inlineStr"/>
       <c r="G134" s="7" t="inlineStr"/>
       <c r="H134" s="7" t="inlineStr"/>
       <c r="I134" s="8" t="inlineStr">
@@ -4321,21 +4321,21 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
+      <c r="D135" s="7" t="inlineStr"/>
+      <c r="E135" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="E135" s="7" t="inlineStr"/>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (G.K)</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="inlineStr"/>
+      <c r="F135" s="7" t="inlineStr"/>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
@@ -4355,28 +4355,28 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="C136" s="7" t="inlineStr"/>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (G.K)</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr"/>
+      <c r="G136" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr"/>
-      <c r="F136" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (G.K)</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="H136" s="7" t="inlineStr"/>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4453,20 +4453,20 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr"/>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="7" t="inlineStr">
         <is>
           <t>L.K.G (EVS)</t>
@@ -4492,31 +4492,35 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (ORAL)</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (EVS)</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr"/>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
-      <c r="H141" s="7" t="inlineStr"/>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr"/>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
       <c r="I141" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4531,31 +4535,35 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ORAL)</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (EVS)</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr"/>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr"/>
-      <c r="H142" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr"/>
       <c r="I142" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4570,39 +4578,31 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr"/>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (ENG)</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (MATH)</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (EVS)</t>
-        </is>
-      </c>
-      <c r="H143" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
+      <c r="H143" s="7" t="inlineStr"/>
       <c r="I143" s="8" t="inlineStr">
         <is>
           <t>L.K.G</t>
@@ -4625,22 +4625,22 @@
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr"/>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ENG)</t>
+          <t>L.K.G (MATH)</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (ORAL)</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>L.K.G (ENG)</t>
-        </is>
-      </c>
+          <t>L.K.G (MATH)</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr"/>
       <c r="H144" s="7" t="inlineStr">
         <is>
           <t>L.K.G (MATH)</t>
@@ -4668,15 +4668,15 @@
           <t>L.K.G (MATH)</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
+      <c r="D145" s="7" t="inlineStr"/>
+      <c r="E145" s="7" t="inlineStr">
         <is>
           <t>L.K.G (ORAL)</t>
         </is>
       </c>
-      <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (MATH)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>L.K.G (EVS)</t>
+          <t>L.K.G (ENG)</t>
         </is>
       </c>
       <c r="I145" s="8" t="inlineStr">
@@ -4769,20 +4769,20 @@
       <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr"/>
-      <c r="I149" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
+      <c r="I149" s="7" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -4796,17 +4796,17 @@
       <c r="E150" s="7" t="inlineStr"/>
       <c r="F150" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H150" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="I150" s="7" t="inlineStr"/>
@@ -4823,20 +4823,20 @@
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr"/>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G151" s="7" t="inlineStr">
+      <c r="I151" s="8" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="I151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -4850,17 +4850,17 @@
       <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G152" s="7" t="inlineStr">
+      <c r="H152" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H152" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="I152" s="7" t="inlineStr"/>
@@ -4882,12 +4882,12 @@
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="I153" s="7" t="inlineStr"/>
@@ -4909,12 +4909,12 @@
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
         </is>
       </c>
       <c r="I154" s="7" t="inlineStr"/>
@@ -4988,24 +4988,24 @@
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr"/>
-      <c r="C158" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="C158" s="7" t="inlineStr"/>
       <c r="D158" s="7" t="inlineStr"/>
       <c r="E158" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="F158" s="7" t="inlineStr">
+      <c r="G158" s="7" t="inlineStr"/>
+      <c r="H158" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="G158" s="7" t="inlineStr"/>
-      <c r="H158" s="7" t="inlineStr"/>
       <c r="I158" s="7" t="inlineStr"/>
     </row>
     <row r="159">
@@ -5019,17 +5019,17 @@
       <c r="D159" s="7" t="inlineStr"/>
       <c r="E159" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="F159" s="7" t="inlineStr">
+      <c r="G159" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr"/>
@@ -5041,25 +5041,25 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B160" s="7" t="inlineStr"/>
-      <c r="C160" s="7" t="inlineStr"/>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
       <c r="D160" s="7" t="inlineStr"/>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
-      <c r="G160" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="H160" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
+      <c r="G160" s="7" t="inlineStr"/>
+      <c r="H160" s="7" t="inlineStr"/>
       <c r="I160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
@@ -5073,19 +5073,19 @@
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="C161" s="7" t="inlineStr"/>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
       <c r="D161" s="7" t="inlineStr"/>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
-      <c r="G161" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
+      <c r="G161" s="7" t="inlineStr"/>
       <c r="H161" s="7" t="inlineStr"/>
       <c r="I161" s="7" t="inlineStr"/>
     </row>
@@ -5096,23 +5096,23 @@
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr"/>
-      <c r="C162" s="7" t="inlineStr"/>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
       <c r="D162" s="7" t="inlineStr"/>
       <c r="E162" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
+      <c r="G162" s="7" t="inlineStr"/>
       <c r="H162" s="7" t="inlineStr"/>
       <c r="I162" s="7" t="inlineStr"/>
     </row>
@@ -5122,17 +5122,17 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B163" s="7" t="inlineStr"/>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
       <c r="C163" s="7" t="inlineStr"/>
       <c r="D163" s="7" t="inlineStr"/>
-      <c r="E163" s="7" t="inlineStr">
+      <c r="E163" s="7" t="inlineStr"/>
+      <c r="F163" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="F163" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr"/>
@@ -5218,12 +5218,12 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
+          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
+          <t>U.K.G (HIN)</t>
         </is>
       </c>
       <c r="E167" s="7" t="inlineStr"/>
@@ -5233,7 +5233,11 @@
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr"/>
-      <c r="H167" s="7" t="inlineStr"/>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
       <c r="I167" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5251,26 +5255,26 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C168" s="7" t="inlineStr">
+      <c r="C168" s="7" t="inlineStr"/>
+      <c r="D168" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="D168" s="7" t="inlineStr"/>
       <c r="E168" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr"/>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
+          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
@@ -5292,26 +5296,26 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>U.K.G (HIN)</t>
+          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr"/>
       <c r="E169" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr"/>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
+          <t>U.K.G (HIN)</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr"/>
       <c r="I169" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5329,28 +5333,24 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C170" s="7" t="inlineStr">
-        <is>
-          <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="D170" s="7" t="inlineStr"/>
-      <c r="E170" s="7" t="inlineStr">
+      <c r="C170" s="7" t="inlineStr"/>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr"/>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="G170" s="7" t="inlineStr"/>
-      <c r="H170" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
+      <c r="H170" s="7" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5368,28 +5368,28 @@
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="C171" s="7" t="inlineStr">
+      <c r="C171" s="7" t="inlineStr"/>
+      <c r="D171" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr">
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
         </is>
       </c>
-      <c r="E171" s="7" t="inlineStr"/>
-      <c r="F171" s="7" t="inlineStr"/>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
+      <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -5410,23 +5410,23 @@
       <c r="C172" s="7" t="inlineStr"/>
       <c r="D172" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="E172" s="7" t="inlineStr">
+      <c r="F172" s="7" t="inlineStr"/>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
         <is>
           <t>U.K.G (HIN)</t>
-        </is>
-      </c>
-      <c r="F172" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr"/>
-      <c r="H172" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="I172" s="8" t="inlineStr">
@@ -5513,22 +5513,18 @@
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D176" s="7" t="inlineStr">
+      <c r="D176" s="7" t="inlineStr"/>
+      <c r="E176" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="E176" s="7" t="inlineStr"/>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr">
-        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
+      <c r="G176" s="7" t="inlineStr"/>
       <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
@@ -5547,27 +5543,23 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C177" s="7" t="inlineStr"/>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr"/>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr">
-        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
+      <c r="G177" s="7" t="inlineStr"/>
       <c r="H177" s="7" t="inlineStr"/>
       <c r="I177" s="8" t="inlineStr">
         <is>
@@ -5586,28 +5578,28 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C178" s="7" t="inlineStr">
+      <c r="C178" s="7" t="inlineStr"/>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr"/>
+      <c r="G178" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="D178" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr"/>
-      <c r="F178" s="7" t="inlineStr">
+      <c r="H178" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5625,24 +5617,28 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C179" s="7" t="inlineStr">
+      <c r="C179" s="7" t="inlineStr"/>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr"/>
-      <c r="F179" s="7" t="inlineStr"/>
-      <c r="G179" s="7" t="inlineStr"/>
-      <c r="H179" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
+      <c r="H179" s="7" t="inlineStr"/>
       <c r="I179" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5662,23 +5658,23 @@
       </c>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="D180" s="7" t="inlineStr">
-        <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="E180" s="7" t="inlineStr"/>
+      <c r="D180" s="7" t="inlineStr"/>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H180" s="7" t="inlineStr"/>
@@ -5699,21 +5695,25 @@
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="C181" s="7" t="inlineStr"/>
-      <c r="D181" s="7" t="inlineStr">
+      <c r="C181" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
+      <c r="D181" s="7" t="inlineStr"/>
       <c r="E181" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="F181" s="7" t="inlineStr"/>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="H181" s="7" t="inlineStr"/>
@@ -5796,7 +5796,7 @@
       <c r="D185" s="7" t="inlineStr"/>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (KAR)</t>
+          <t>Class 9 (KAR)</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
@@ -5820,7 +5820,11 @@
       <c r="E186" s="7" t="inlineStr"/>
       <c r="F186" s="7" t="inlineStr"/>
       <c r="G186" s="7" t="inlineStr"/>
-      <c r="H186" s="7" t="inlineStr"/>
+      <c r="H186" s="7" t="inlineStr">
+        <is>
+          <t>Class 1 (KAR)</t>
+        </is>
+      </c>
       <c r="I186" s="7" t="inlineStr"/>
     </row>
     <row r="187">
@@ -5830,13 +5834,13 @@
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr"/>
-      <c r="C187" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (KAR)</t>
-        </is>
-      </c>
+      <c r="C187" s="7" t="inlineStr"/>
       <c r="D187" s="7" t="inlineStr"/>
-      <c r="E187" s="7" t="inlineStr"/>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (KAR)</t>
+        </is>
+      </c>
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr"/>
       <c r="H187" s="7" t="inlineStr"/>
@@ -5851,11 +5855,15 @@
       <c r="B188" s="7" t="inlineStr"/>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (KAR)</t>
+          <t>Class 6 (KAR)</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr"/>
-      <c r="E188" s="7" t="inlineStr"/>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (KAR)</t>
+        </is>
+      </c>
       <c r="F188" s="7" t="inlineStr"/>
       <c r="G188" s="7" t="inlineStr"/>
       <c r="H188" s="7" t="inlineStr"/>
@@ -5869,18 +5877,22 @@
       </c>
       <c r="B189" s="7" t="inlineStr"/>
       <c r="C189" s="7" t="inlineStr"/>
-      <c r="D189" s="7" t="inlineStr"/>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (KAR)</t>
+        </is>
+      </c>
       <c r="E189" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (KAR)</t>
-        </is>
-      </c>
-      <c r="F189" s="7" t="inlineStr"/>
-      <c r="G189" s="7" t="inlineStr">
+          <t>Class 5 (KAR)</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
         <is>
           <t>Class 2 (KAR)</t>
         </is>
       </c>
+      <c r="G189" s="7" t="inlineStr"/>
       <c r="H189" s="7" t="inlineStr"/>
       <c r="I189" s="7" t="inlineStr"/>
     </row>
@@ -5891,24 +5903,16 @@
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr"/>
-      <c r="C190" s="7" t="inlineStr"/>
+      <c r="C190" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (KAR)</t>
+        </is>
+      </c>
       <c r="D190" s="7" t="inlineStr"/>
-      <c r="E190" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (KAR)</t>
-        </is>
-      </c>
+      <c r="E190" s="7" t="inlineStr"/>
       <c r="F190" s="7" t="inlineStr"/>
-      <c r="G190" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (KAR)</t>
-        </is>
-      </c>
-      <c r="H190" s="7" t="inlineStr">
-        <is>
-          <t>Class 1 (KAR)</t>
-        </is>
-      </c>
+      <c r="G190" s="7" t="inlineStr"/>
+      <c r="H190" s="7" t="inlineStr"/>
       <c r="I190" s="7" t="inlineStr"/>
     </row>
     <row r="192">
@@ -5986,14 +5990,10 @@
       <c r="F194" s="7" t="inlineStr"/>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H194" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (P.E.T)</t>
-        </is>
-      </c>
+          <t>Class 3 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr"/>
       <c r="I194" s="7" t="inlineStr"/>
     </row>
     <row r="195">
@@ -6007,12 +6007,12 @@
       <c r="D195" s="7" t="inlineStr"/>
       <c r="E195" s="7" t="inlineStr"/>
       <c r="F195" s="7" t="inlineStr"/>
-      <c r="G195" s="7" t="inlineStr"/>
-      <c r="H195" s="7" t="inlineStr">
+      <c r="G195" s="7" t="inlineStr">
         <is>
           <t>Class 5 (P.E.T)</t>
         </is>
       </c>
+      <c r="H195" s="7" t="inlineStr"/>
       <c r="I195" s="7" t="inlineStr"/>
     </row>
     <row r="196">
@@ -6028,10 +6028,14 @@
       <c r="F196" s="7" t="inlineStr"/>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H196" s="7" t="inlineStr"/>
+          <t>Class 10 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H196" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (P.E.T)</t>
+        </is>
+      </c>
       <c r="I196" s="7" t="inlineStr"/>
     </row>
     <row r="197">
@@ -6045,12 +6049,12 @@
       <c r="D197" s="7" t="inlineStr"/>
       <c r="E197" s="7" t="inlineStr"/>
       <c r="F197" s="7" t="inlineStr"/>
-      <c r="G197" s="7" t="inlineStr">
+      <c r="G197" s="7" t="inlineStr"/>
+      <c r="H197" s="7" t="inlineStr">
         <is>
           <t>Class 5 (P.E.T)</t>
         </is>
       </c>
-      <c r="H197" s="7" t="inlineStr"/>
       <c r="I197" s="7" t="inlineStr"/>
     </row>
     <row r="198">
@@ -6222,7 +6226,7 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -6300,19 +6304,19 @@
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -6329,44 +6333,44 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
       <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(CHEM)</t>
+        </is>
+      </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(PHY)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -6377,14 +6381,14 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(EVS)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -6395,8 +6399,8 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -6413,32 +6417,32 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
+(PHY)</t>
+        </is>
+      </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(CHEM)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -6455,8 +6459,8 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SITHA
+(MATH)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -6468,61 +6472,61 @@
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>MARTIAL ARTS
 (KAR)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -6557,8 +6561,8 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -6569,32 +6573,32 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(CHEM)</t>
+          <t>SANGEETHA
+(COMP)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -6617,40 +6621,40 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
@@ -6659,26 +6663,25 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -6701,62 +6704,62 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -6832,10 +6835,9 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6853,7 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -6916,8 +6918,8 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>BHEEMA
-(CHEM)</t>
+          <t>GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -6929,13 +6931,13 @@
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -6946,44 +6948,44 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>BHAVANI
+(G.K)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>LALITHA
+(PHY)</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(GRAM)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -7007,45 +7009,45 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
           <t>RAVI
@@ -7066,14 +7068,14 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
           <t>BHEEMA
 (CHEM)</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -7084,73 +7086,74 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SITHA
+(EVS)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
+          <t>BHAVANI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -7162,73 +7165,73 @@
       <c r="C14" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -7239,74 +7242,74 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ORAL)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -7317,56 +7320,56 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SITHA
+(EVS)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>BHAVANI
+(EVS)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(EVS)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>P.E
-(P.E.T)</t>
-        </is>
-      </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(BIO)</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>FATHIMA
-(HIN)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -7377,14 +7380,14 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
           <t>SONU
 (ENG)</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7481,7 @@
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -7543,8 +7546,8 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -7561,8 +7564,8 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -7573,22 +7576,22 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
@@ -7597,26 +7600,26 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
           <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>BHEEMA
 (PHY)</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
@@ -7634,7 +7637,7 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -7645,44 +7648,44 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
       <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>RAVI
 (ENG)</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -7711,73 +7714,74 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SITHA
+(MATH)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
+          <t>LALITHA
+(BIO)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
           <t>RAVI
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
-(COMP)</t>
-        </is>
-      </c>
-      <c r="M21" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
     </row>
@@ -7789,19 +7793,19 @@
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(EVS)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(ENG)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -7812,50 +7816,50 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
-        </is>
-      </c>
       <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -7866,74 +7870,74 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>P.E
 (P.E.T)</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(COMP)</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>SONU
-(ENG)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -7944,74 +7948,74 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>P.E
+(P.E.T)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
       <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -8087,9 +8091,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N25" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8110,7 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -8123,7 +8128,7 @@
       <c r="F26" s="7" t="inlineStr">
         <is>
           <t>SAI LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -8188,8 +8193,8 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -8200,14 +8205,14 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>TULASI
-(MATH)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -8224,32 +8229,32 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
         </is>
       </c>
     </row>
@@ -8266,68 +8271,68 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(MATH)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>D.V.RAO
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -8338,32 +8343,32 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(MATH)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -8374,8 +8379,8 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
@@ -8386,26 +8391,26 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(PHY)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -8417,13 +8422,13 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -8440,50 +8445,50 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(EVS)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>LALITHA
+(CHEM)</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>RAVI
+(GRAM)</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -8495,49 +8500,49 @@
       <c r="C31" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SAI LAKSHMI
+(HIN)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
           <t>MAHA
-(GRAM)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>P.E
-(P.E.T)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
           <t>LALITHA
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -8548,20 +8553,19 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
           <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
+      <c r="N31" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8572,74 +8576,74 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>SITHA
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>P.E
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(BIO)</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -8798,8 +8802,8 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -8816,44 +8820,44 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>BHAVANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(GRAM)</t>
+        </is>
+      </c>
       <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
-(TEL)</t>
-        </is>
-      </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(CHEM)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
@@ -8864,14 +8868,14 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>BHEEMA
+(PHY)</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
@@ -8888,46 +8892,46 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SITHA
+(MATH)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(HIN)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>BHAVANI
+(MATH)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
@@ -8936,25 +8940,26 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>LALITHA
+(CHEM)</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
 (CHEM)</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr">
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N36" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8966,37 +8971,37 @@
       <c r="C37" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>TULASI
+(MATH)</t>
+        </is>
+      </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>MAHA
-(ENG)</t>
+          <t>LALITHA
+(EVS)</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>PALLAVI
-(SOC)</t>
+          <t>SWATHI
+(TEL)</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -9013,14 +9018,14 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(CHEM)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -9031,8 +9036,8 @@
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9049,7 @@
       <c r="C38" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -9055,62 +9060,62 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
+          <t>SAI LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>MARTIAL ARTS
+(KAR)</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
           <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>NAGAMANI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>SANGEETHA
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
 (G.K)</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>RAVI
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>SONU
 (ENG)</t>
         </is>
       </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="N38" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9121,14 +9126,14 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ENG)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
+          <t>SWATHI
+(HIN)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -9139,8 +9144,8 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -9151,44 +9156,44 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>TULASI
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -9205,44 +9210,44 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
       <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
@@ -9253,20 +9258,20 @@
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>SONU
+(ENG)</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>RAVI
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9377,7 @@
       <c r="E42" s="7" t="inlineStr">
         <is>
           <t>NAGAMANI
-(TEL)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -9425,8 +9430,8 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>GOWTHAM
-(MATH)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -9443,56 +9448,56 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>NAGAMANI
-(TEL)</t>
+          <t>SAI LAKSHMI
+(ENG)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>SAI LAKSHMI
-(HIN)</t>
+          <t>MAHESWARI
+(COMP)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>BHAVANI
-(G.K)</t>
+          <t>MAHA
+(ENG)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>LALITHA
-(BIO)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>MARTIAL ARTS
+(KAR)</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
           <t>BHEEMA
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -9501,9 +9506,10 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="N43" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -9514,8 +9520,8 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>SITHA
-(ORAL)</t>
+          <t>NAGAMANI
+(TEL)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -9526,44 +9532,44 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
+          <t>MAHA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>PALLAVI
+(SOC)</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
 (EVS)</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(GRAM)</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>TULASI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>SWATHI
 (TEL)</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(MATH)</t>
+          <t>FATHIMA
+(HIN)</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -9574,14 +9580,14 @@
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
+          <t>BHEEMA
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
           <t>GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="inlineStr">
-        <is>
-          <t>BHEEMA
-(PHY)</t>
         </is>
       </c>
     </row>
@@ -9592,62 +9598,62 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
+          <t>SITHA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
           <t>NAGAMANI
 (TEL)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>BHAVANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>LALITHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>SWATHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>MAHESWARI
-(COMP)</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>FATHIMA
 (HIN)</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
           <t>RAVI
-(ENG)</t>
+(GRAM)</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>SANGEETHA
+(MATH)</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -9656,10 +9662,9 @@
 (HIN)</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr">
-        <is>
-          <t>D.V.RAO
-(TEL)</t>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9671,61 +9676,61 @@
       <c r="C46" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>SAI LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>SAI LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>MAHESWARI
-(COMP)</t>
+          <t>TULASI
+(MATH)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>SANGEETHA
-(G.K)</t>
+          <t>PALLAVI
+(SOC)</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>SWATHI
-(TEL)</t>
+          <t>LALITHA
+(PHY)</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>D.V.RAO
-(TEL)</t>
+          <t>RAVI
+(ENG)</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -9734,10 +9739,9 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="N46" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
+      <c r="N46" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9754,68 +9758,67 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
+          <t>NAGAMANI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
           <t>BHAVANI
 (MATH)</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>MAHESWARI
 (COMP)</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>MAHA
-(ENG)</t>
-        </is>
-      </c>
       <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>PALLAVI
-(SOC)</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>TULASI
 (MATH)</t>
         </is>
       </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>MAHA
+(GRAM)</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>SWATHI
+(TEL)</t>
+        </is>
+      </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>RAVI
-(ENG)</t>
+          <t>LALITHA
+(CHEM)</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>SANGEETHA
 (MATH)</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>SONU
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M47" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>SONU
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -9827,19 +9830,19 @@
       <c r="C48" s="7" t="inlineStr">
         <is>
           <t>SITHA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
+          <t>SWATHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
           <t>SAI LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>MARTIAL ARTS
-(KAR)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -9850,49 +9853,50 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
+          <t>MAHESWARI
+(COMP)</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
           <t>MAHA
 (ENG)</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>FATHIMA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>PALLAVI
 (SOC)</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>SWATHI
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>D.V.RAO
 (TEL)</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>LALITHA
-(PHY)</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>FATHIMA
-(HIN)</t>
-        </is>
-      </c>
       <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>SANGEETHA
+(COMP)</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
         <is>
           <t>SONU
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N48" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
